--- a/test.xlsx
+++ b/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Documents\Meerkat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C1B2A1-FF88-4182-87EE-114A52E12057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92B811F-3977-48C3-855D-06419CFB077F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="3420" yWindow="3135" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2965" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2966" uniqueCount="1199">
   <si>
     <t>N° Cde</t>
   </si>
@@ -4177,6 +4177,10 @@
 En Cours - 17/04/2025 13:18
 Simon MASURIER :
 Terminé - 17/04/2025 13:18</t>
+  </si>
+  <si>
+    <t>Simon MASURIER :
+En Cours - 17/04/2025 14:58</t>
   </si>
 </sst>
 </file>
@@ -4351,7 +4355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
@@ -4543,6 +4547,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5153,8 +5160,10 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" s="11"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="12"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="12">
+        <v>45764</v>
+      </c>
       <c r="Q5" s="13"/>
       <c r="R5" s="14" t="s">
         <v>29</v>
@@ -5163,7 +5172,9 @@
         <v>1196</v>
       </c>
       <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
+      <c r="U5" s="14">
+        <v>45764.623726851853</v>
+      </c>
       <c r="V5" s="15" t="s">
         <v>30</v>
       </c>
@@ -5171,7 +5182,9 @@
         <v>1197</v>
       </c>
       <c r="X5" s="15"/>
-      <c r="Y5" s="15"/>
+      <c r="Y5" s="15" t="s">
+        <v>1198</v>
+      </c>
     </row>
     <row r="6" spans="1:25" s="16" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7">

--- a/test.xlsx
+++ b/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Documents\Meerkat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{A771A05B-0B84-4248-B0CE-426989597E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{2754DE37-360C-4CC1-A1D2-C58EBC97763E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="1125" yWindow="1125" windowWidth="38700" windowHeight="15345" xr2:uid="{EB84704D-40C6-4DE5-9D9A-A41F237B8341}"/>
   </bookViews>
@@ -869,15 +869,15 @@
   <calcPr calcId="191029"/>
   <customWorkbookViews>
     <customWorkbookView name="simon masurier - Affichage personnalisé" guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" mergeInterval="0" personalView="1" minimized="1" windowWidth="0" windowHeight="0" activeSheetId="1"/>
+    <customWorkbookView name="Atelier - Affichage personnalisé" guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1696" windowHeight="1026" activeSheetId="1"/>
+    <customWorkbookView name="Production - Affichage personnalisé" guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}" mergeInterval="0" personalView="1" minimized="1" windowWidth="0" windowHeight="0" activeSheetId="1"/>
+    <customWorkbookView name="COMPTA1 - Affichage personnalisé" guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="COMPTA2 - Affichage personnalisé" guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="SAEMT - Affichage personnalisé" guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}" mergeInterval="0" personalView="1" maximized="1" xWindow="-9" yWindow="-9" windowWidth="1938" windowHeight="1048" activeSheetId="1"/>
+    <customWorkbookView name="Commercial Commercial - Affichage personnalisé" guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1696" windowHeight="1026" activeSheetId="1"/>
+    <customWorkbookView name="CEDRIC - Affichage personnalisé" guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}" mergeInterval="0" personalView="1" xWindow="873" yWindow="141" windowWidth="1874" windowHeight="1096" activeSheetId="1"/>
+    <customWorkbookView name="SYLVAIN - Affichage personnalisé" guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
     <customWorkbookView name="YOANN - Affichage personnalisé" guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}" autoUpdate="1" mergeInterval="15" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
-    <customWorkbookView name="SYLVAIN - Affichage personnalisé" guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
-    <customWorkbookView name="CEDRIC - Affichage personnalisé" guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}" mergeInterval="0" personalView="1" xWindow="873" yWindow="141" windowWidth="1874" windowHeight="1096" activeSheetId="1"/>
-    <customWorkbookView name="Commercial Commercial - Affichage personnalisé" guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1696" windowHeight="1026" activeSheetId="1"/>
-    <customWorkbookView name="SAEMT - Affichage personnalisé" guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}" mergeInterval="0" personalView="1" maximized="1" xWindow="-9" yWindow="-9" windowWidth="1938" windowHeight="1048" activeSheetId="1"/>
-    <customWorkbookView name="COMPTA2 - Affichage personnalisé" guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="COMPTA1 - Affichage personnalisé" guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Production - Affichage personnalisé" guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}" mergeInterval="0" personalView="1" minimized="1" windowWidth="0" windowHeight="0" activeSheetId="1"/>
-    <customWorkbookView name="Atelier - Affichage personnalisé" guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1696" windowHeight="1026" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4686,7 +4686,7 @@
 </file>
 
 <file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{A285D050-1DCA-420E-9447-DAE3F1DC296A}" diskRevisions="1" revisionId="125974" version="19">
+<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{6B126993-1D9B-477D-A59F-F40D6AD1695D}" diskRevisions="1" revisionId="125975" version="20">
   <header guid="{5369C422-BCF9-41A0-ACD4-6F1F3AA60B78}" dateTime="2025-04-17T18:17:38" maxSheetId="3" userName="simon masurier" r:id="rId10733">
     <sheetIdMap count="2">
       <sheetId val="1"/>
@@ -4790,6 +4790,12 @@
     </sheetIdMap>
   </header>
   <header guid="{A285D050-1DCA-420E-9447-DAE3F1DC296A}" dateTime="2025-04-17T18:45:21" maxSheetId="3" userName="simon masurier" r:id="rId10750" minRId="125967" maxRId="125973">
+    <sheetIdMap count="2">
+      <sheetId val="1"/>
+      <sheetId val="2"/>
+    </sheetIdMap>
+  </header>
+  <header guid="{6B126993-1D9B-477D-A59F-F40D6AD1695D}" dateTime="2025-04-17T19:01:54" maxSheetId="3" userName="simon masurier" r:id="rId10751">
     <sheetIdMap count="2">
       <sheetId val="1"/>
       <sheetId val="2"/>
@@ -5184,6 +5190,17 @@
       </is>
     </nc>
   </rcc>
+  <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="delete"/>
+  <rdn rId="0" localSheetId="1" customView="1" name="Z_FC992F80_D491_44A2_9044_1F3C55C8B0BF_.wvu.FilterData" hidden="1" oldHidden="1">
+    <formula>'Planning prod'!$A$2:$P$413</formula>
+    <oldFormula>'Planning prod'!$A$2:$P$413</oldFormula>
+  </rdn>
+  <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="add"/>
+</revisions>
+</file>
+
+<file path=xl/revisions/revisionLog18.xml><?xml version="1.0" encoding="utf-8"?>
+<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="delete"/>
   <rdn rId="0" localSheetId="1" customView="1" name="Z_FC992F80_D491_44A2_9044_1F3C55C8B0BF_.wvu.FilterData" hidden="1" oldHidden="1">
     <formula>'Planning prod'!$A$2:$P$413</formula>
@@ -58754,59 +58771,59 @@
       <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
       <autoFilter ref="A2:P413" xr:uid="{7722E3C6-80F5-4991-A518-5F8966A312D6}"/>
     </customSheetView>
-    <customSheetView guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}" scale="120" showAutoFilter="1" topLeftCell="C1">
-      <selection activeCell="L1" sqref="L1"/>
+    <customSheetView guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}" scale="120" showPageBreaks="1" showAutoFilter="1" topLeftCell="A400">
+      <selection activeCell="A424" sqref="A424:XFD424"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId2"/>
-      <autoFilter ref="A2:P413" xr:uid="{7B2C4991-9923-4FF0-B5F0-2F21735442B1}"/>
+      <autoFilter ref="A2:P413" xr:uid="{CBD38F64-AAEE-4E94-B914-ECBAC001FCFD}"/>
     </customSheetView>
-    <customSheetView guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}" scale="90" showAutoFilter="1" topLeftCell="D124">
-      <selection activeCell="I150" sqref="I150"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="8" orientation="landscape" r:id="rId3"/>
-      <autoFilter ref="A2:P473" xr:uid="{FF4C83F2-D247-4B94-A282-34B0FFCAD592}"/>
+    <customSheetView guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}" showPageBreaks="1" fitToPage="1" showAutoFilter="1" topLeftCell="A467">
+      <selection activeCell="E464" sqref="E464"/>
+      <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="8" scale="10" fitToHeight="0" orientation="portrait" r:id="rId3"/>
+      <autoFilter ref="A1:P364" xr:uid="{EE701B42-1FC3-41F9-82C2-ADF42BE22A03}"/>
     </customSheetView>
-    <customSheetView guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}" scale="120" showAutoFilter="1" topLeftCell="A373">
-      <selection activeCell="A394" sqref="A394:D394"/>
+    <customSheetView guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}" scale="120" showAutoFilter="1">
+      <pane ySplit="1" topLeftCell="A168" activePane="bottomLeft" state="frozen"/>
+      <selection pane="bottomLeft" activeCell="A149" sqref="A149:XFD149"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId4"/>
-      <autoFilter ref="A2:P386" xr:uid="{261D8C8D-F8EC-4822-B56E-B8786CAF2FB7}"/>
+      <autoFilter ref="A2:P377" xr:uid="{7F560AD7-0201-4CDF-A810-2721661A43C5}"/>
     </customSheetView>
-    <customSheetView guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}" scale="120" topLeftCell="C211">
-      <selection activeCell="G234" sqref="G234"/>
+    <customSheetView guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}" scale="120" showAutoFilter="1" topLeftCell="A444">
+      <selection activeCell="E482" sqref="E482"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId5"/>
+      <autoFilter ref="A2:P514" xr:uid="{FFC7520C-A177-472F-8DAE-99A29FD6B980}"/>
     </customSheetView>
     <customSheetView guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}" showAutoFilter="1" topLeftCell="C391">
       <selection activeCell="J487" sqref="J487"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId6"/>
-      <autoFilter ref="A1:P535" xr:uid="{19FBAA90-E4B5-4B0B-A74F-A26A72F6B40C}"/>
+      <autoFilter ref="A1:P535" xr:uid="{4DDD486C-1573-4711-8EEC-3685D12668C0}"/>
     </customSheetView>
-    <customSheetView guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}" scale="120" showAutoFilter="1" topLeftCell="A444">
-      <selection activeCell="E482" sqref="E482"/>
+    <customSheetView guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}" scale="120" topLeftCell="C211">
+      <selection activeCell="G234" sqref="G234"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId7"/>
-      <autoFilter ref="A2:P514" xr:uid="{8F0DDB68-47A4-49BB-8CAA-47F873DD93A2}"/>
     </customSheetView>
-    <customSheetView guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}" scale="120" showAutoFilter="1">
-      <pane ySplit="1" topLeftCell="A168" activePane="bottomLeft" state="frozen"/>
-      <selection pane="bottomLeft" activeCell="A149" sqref="A149:XFD149"/>
+    <customSheetView guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}" scale="120" showAutoFilter="1" topLeftCell="A373">
+      <selection activeCell="A394" sqref="A394:D394"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId8"/>
-      <autoFilter ref="A2:P377" xr:uid="{9801D8EA-9D53-4365-9053-B5884AF97D63}"/>
+      <autoFilter ref="A2:P386" xr:uid="{89645BF1-C938-4B8B-B712-B40AAAB78240}"/>
     </customSheetView>
-    <customSheetView guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}" showPageBreaks="1" fitToPage="1" showAutoFilter="1" topLeftCell="A467">
-      <selection activeCell="E464" sqref="E464"/>
-      <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="8" scale="10" fitToHeight="0" orientation="portrait" r:id="rId9"/>
-      <autoFilter ref="A1:P364" xr:uid="{4F1B99FE-D4D9-4541-BAAC-2AC9F9C58CD1}"/>
+    <customSheetView guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}" scale="90" showAutoFilter="1" topLeftCell="D124">
+      <selection activeCell="I150" sqref="I150"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="8" orientation="landscape" r:id="rId9"/>
+      <autoFilter ref="A2:P473" xr:uid="{81DBA132-B41A-4698-BBE7-2067C949E13F}"/>
     </customSheetView>
-    <customSheetView guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}" scale="120" showPageBreaks="1" showAutoFilter="1" topLeftCell="A400">
-      <selection activeCell="A424" sqref="A424:XFD424"/>
+    <customSheetView guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}" scale="120" showAutoFilter="1" topLeftCell="C1">
+      <selection activeCell="L1" sqref="L1"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId10"/>
-      <autoFilter ref="A2:P413" xr:uid="{7D797CC2-56E7-4A45-AC1F-FDC0B14ABFB3}"/>
+      <autoFilter ref="A2:P413" xr:uid="{BD5EE145-0813-46A7-BC75-B92AD019CB7F}"/>
     </customSheetView>
   </customSheetViews>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -58875,7 +58892,31 @@
       <selection sqref="A1:D5"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
-    <customSheetView guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}">
+    <customSheetView guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}">
       <selection sqref="A1:D5"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
@@ -58883,31 +58924,7 @@
       <selection sqref="A1:D5"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
-    <customSheetView guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}">
+    <customSheetView guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}">
       <selection sqref="A1:D5"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>

--- a/test.xlsx
+++ b/test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Documents\Meerkat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{2754DE37-360C-4CC1-A1D2-C58EBC97763E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{56E75DFE-D236-4157-BB8E-71D06E06640A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1125" yWindow="1125" windowWidth="38700" windowHeight="15345" xr2:uid="{EB84704D-40C6-4DE5-9D9A-A41F237B8341}"/>
+    <workbookView minimized="1" xWindow="3900" yWindow="3900" windowWidth="38700" windowHeight="15345" xr2:uid="{EB84704D-40C6-4DE5-9D9A-A41F237B8341}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning prod" sheetId="1" r:id="rId1"/>
@@ -897,7 +897,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5178" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5179" uniqueCount="990">
   <si>
     <t>N° Cde</t>
   </si>
@@ -4193,10 +4193,21 @@
 Terminé - 17/04/2025 18:45</t>
   </si>
   <si>
+    <t>1 h 59 m</t>
+  </si>
+  <si>
     <t>Simon MASURIER :
 En Cours - 17/04/2025 18:43
 Simon MASURIER :
-En Cours - 17/04/2025 18:45</t>
+Terminé - 17/04/2025 20:43</t>
+  </si>
+  <si>
+    <t>Simon MASURIER :
+En Cours - 17/04/2025 18:43
+Simon MASURIER :
+En Cours - 17/04/2025 18:45
+Simon MASURIER :
+En Cours - 17/04/2025 20:43</t>
   </si>
   <si>
     <t xml:space="preserve">Simon MASURIER :
@@ -4686,7 +4697,7 @@
 </file>
 
 <file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{6B126993-1D9B-477D-A59F-F40D6AD1695D}" diskRevisions="1" revisionId="125975" version="20">
+<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{1E54D5B1-1A9D-45B0-B660-700E91D70786}" diskRevisions="1" revisionId="125982" version="22">
   <header guid="{5369C422-BCF9-41A0-ACD4-6F1F3AA60B78}" dateTime="2025-04-17T18:17:38" maxSheetId="3" userName="simon masurier" r:id="rId10733">
     <sheetIdMap count="2">
       <sheetId val="1"/>
@@ -4796,6 +4807,18 @@
     </sheetIdMap>
   </header>
   <header guid="{6B126993-1D9B-477D-A59F-F40D6AD1695D}" dateTime="2025-04-17T19:01:54" maxSheetId="3" userName="simon masurier" r:id="rId10751">
+    <sheetIdMap count="2">
+      <sheetId val="1"/>
+      <sheetId val="2"/>
+    </sheetIdMap>
+  </header>
+  <header guid="{88D4AFF2-5DED-4E38-BD85-6AD913965270}" dateTime="2025-04-17T20:43:33" maxSheetId="3" userName="simon masurier" r:id="rId10752">
+    <sheetIdMap count="2">
+      <sheetId val="1"/>
+      <sheetId val="2"/>
+    </sheetIdMap>
+  </header>
+  <header guid="{1E54D5B1-1A9D-45B0-B660-700E91D70786}" dateTime="2025-04-17T20:43:42" maxSheetId="3" userName="simon masurier" r:id="rId10753" minRId="125977" maxRId="125981">
     <sheetIdMap count="2">
       <sheetId val="1"/>
       <sheetId val="2"/>
@@ -5210,8 +5233,109 @@
 </revisions>
 </file>
 
+<file path=xl/revisions/revisionLog19.xml><?xml version="1.0" encoding="utf-8"?>
+<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="delete"/>
+  <rdn rId="0" localSheetId="1" customView="1" name="Z_FC992F80_D491_44A2_9044_1F3C55C8B0BF_.wvu.FilterData" hidden="1" oldHidden="1">
+    <formula>'Planning prod'!$A$2:$P$413</formula>
+    <oldFormula>'Planning prod'!$A$2:$P$413</oldFormula>
+  </rdn>
+  <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="add"/>
+</revisions>
+</file>
+
 <file path=xl/revisions/revisionLog2.xml><?xml version="1.0" encoding="utf-8"?>
 <revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="delete"/>
+  <rdn rId="0" localSheetId="1" customView="1" name="Z_FC992F80_D491_44A2_9044_1F3C55C8B0BF_.wvu.FilterData" hidden="1" oldHidden="1">
+    <formula>'Planning prod'!$A$2:$P$413</formula>
+    <oldFormula>'Planning prod'!$A$2:$P$413</oldFormula>
+  </rdn>
+  <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="add"/>
+</revisions>
+</file>
+
+<file path=xl/revisions/revisionLog20.xml><?xml version="1.0" encoding="utf-8"?>
+<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <rfmt sheetId="1" sqref="O3" start="0" length="0">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </rfmt>
+  <rcc rId="125977" sId="1" numFmtId="27">
+    <oc r="U3">
+      <v>45764.780451388891</v>
+    </oc>
+    <nc r="U3" t="inlineStr">
+      <is>
+        <t>1 h 59 m</t>
+      </is>
+    </nc>
+  </rcc>
+  <rcc rId="125978" sId="1">
+    <oc r="Y3" t="inlineStr">
+      <is>
+        <t>Simon MASURIER :
+En Cours - 17/04/2025 18:43</t>
+      </is>
+    </oc>
+    <nc r="Y3" t="inlineStr">
+      <is>
+        <t>Simon MASURIER :
+En Cours - 17/04/2025 18:43
+Simon MASURIER :
+Terminé - 17/04/2025 20:43</t>
+      </is>
+    </nc>
+  </rcc>
+  <rcc rId="125979" sId="1" numFmtId="27">
+    <oc r="W4">
+      <v>45764.781493055554</v>
+    </oc>
+    <nc r="W4">
+      <v>45764.863680555558</v>
+    </nc>
+  </rcc>
+  <rcc rId="125980" sId="1">
+    <oc r="AA4" t="inlineStr">
+      <is>
+        <t>Simon MASURIER :
+En Cours - 17/04/2025 18:43
+Simon MASURIER :
+En Cours - 17/04/2025 18:45</t>
+      </is>
+    </oc>
+    <nc r="AA4" t="inlineStr">
+      <is>
+        <t>Simon MASURIER :
+En Cours - 17/04/2025 18:43
+Simon MASURIER :
+En Cours - 17/04/2025 18:45
+Simon MASURIER :
+En Cours - 17/04/2025 20:43</t>
+      </is>
+    </nc>
+  </rcc>
+  <rcc rId="125981" sId="1">
+    <oc r="AA5" t="inlineStr">
+      <is>
+        <t xml:space="preserve">Simon MASURIER :
+Terminé - 17/04/2025 18:18
+</t>
+      </is>
+    </oc>
+    <nc r="AA5" t="inlineStr">
+      <is>
+        <t xml:space="preserve">Simon MASURIER :
+Terminé - 17/04/2025 18:18
+</t>
+      </is>
+    </nc>
+  </rcc>
   <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="delete"/>
   <rdn rId="0" localSheetId="1" customView="1" name="Z_FC992F80_D491_44A2_9044_1F3C55C8B0BF_.wvu.FilterData" hidden="1" oldHidden="1">
     <formula>'Planning prod'!$A$2:$P$413</formula>
@@ -6186,7 +6310,7 @@
         <v>45572</v>
       </c>
       <c r="N3" s="77"/>
-      <c r="O3" s="78"/>
+      <c r="O3" s="77"/>
       <c r="P3" s="49"/>
       <c r="Q3" s="49"/>
       <c r="R3" s="10"/>
@@ -6194,8 +6318,8 @@
       <c r="T3" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="U3" s="11">
-        <v>45764.780451388891</v>
+      <c r="U3" s="11" t="s">
+        <v>986</v>
       </c>
       <c r="V3" s="12"/>
       <c r="W3" s="12"/>
@@ -6203,7 +6327,7 @@
         <v>985</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="Z3" s="12"/>
       <c r="AA3" s="12"/>
@@ -6259,7 +6383,7 @@
       </c>
       <c r="V4" s="12"/>
       <c r="W4" s="11">
-        <v>45764.781493055554</v>
+        <v>45764.863680555558</v>
       </c>
       <c r="X4" s="12" t="s">
         <v>985</v>
@@ -6269,7 +6393,7 @@
       </c>
       <c r="Z4" s="12"/>
       <c r="AA4" s="12" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="5" spans="1:27" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -6339,7 +6463,7 @@
         <v>983</v>
       </c>
       <c r="AA5" s="12" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="6" spans="1:27" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -58775,32 +58899,32 @@
       <selection activeCell="A424" sqref="A424:XFD424"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId2"/>
-      <autoFilter ref="A2:P413" xr:uid="{CBD38F64-AAEE-4E94-B914-ECBAC001FCFD}"/>
+      <autoFilter ref="A2:P413" xr:uid="{FA5FB3DF-CAA0-465A-AD54-2532FA7DD625}"/>
     </customSheetView>
     <customSheetView guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}" showPageBreaks="1" fitToPage="1" showAutoFilter="1" topLeftCell="A467">
       <selection activeCell="E464" sqref="E464"/>
       <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" scale="10" fitToHeight="0" orientation="portrait" r:id="rId3"/>
-      <autoFilter ref="A1:P364" xr:uid="{EE701B42-1FC3-41F9-82C2-ADF42BE22A03}"/>
+      <autoFilter ref="A1:P364" xr:uid="{419441F1-66DA-474B-B1B5-36220848907E}"/>
     </customSheetView>
     <customSheetView guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}" scale="120" showAutoFilter="1">
       <pane ySplit="1" topLeftCell="A168" activePane="bottomLeft" state="frozen"/>
       <selection pane="bottomLeft" activeCell="A149" sqref="A149:XFD149"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId4"/>
-      <autoFilter ref="A2:P377" xr:uid="{7F560AD7-0201-4CDF-A810-2721661A43C5}"/>
+      <autoFilter ref="A2:P377" xr:uid="{620022E2-B9E4-43FE-B77D-7A1C1310119F}"/>
     </customSheetView>
     <customSheetView guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}" scale="120" showAutoFilter="1" topLeftCell="A444">
       <selection activeCell="E482" sqref="E482"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId5"/>
-      <autoFilter ref="A2:P514" xr:uid="{FFC7520C-A177-472F-8DAE-99A29FD6B980}"/>
+      <autoFilter ref="A2:P514" xr:uid="{947DE699-CD34-422C-B707-1BEFE9DDDBA3}"/>
     </customSheetView>
     <customSheetView guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}" showAutoFilter="1" topLeftCell="C391">
       <selection activeCell="J487" sqref="J487"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId6"/>
-      <autoFilter ref="A1:P535" xr:uid="{4DDD486C-1573-4711-8EEC-3685D12668C0}"/>
+      <autoFilter ref="A1:P535" xr:uid="{4AC187BA-5ACF-4F62-AE62-8E7120B1CCCD}"/>
     </customSheetView>
     <customSheetView guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}" scale="120" topLeftCell="C211">
       <selection activeCell="G234" sqref="G234"/>
@@ -58811,19 +58935,19 @@
       <selection activeCell="A394" sqref="A394:D394"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId8"/>
-      <autoFilter ref="A2:P386" xr:uid="{89645BF1-C938-4B8B-B712-B40AAAB78240}"/>
+      <autoFilter ref="A2:P386" xr:uid="{19AF686C-2C7A-4DDD-8100-72C2D0C4E56D}"/>
     </customSheetView>
     <customSheetView guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}" scale="90" showAutoFilter="1" topLeftCell="D124">
       <selection activeCell="I150" sqref="I150"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId9"/>
-      <autoFilter ref="A2:P473" xr:uid="{81DBA132-B41A-4698-BBE7-2067C949E13F}"/>
+      <autoFilter ref="A2:P473" xr:uid="{58505C7A-7A70-4667-B2AE-A99094DE10BE}"/>
     </customSheetView>
     <customSheetView guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}" scale="120" showAutoFilter="1" topLeftCell="C1">
       <selection activeCell="L1" sqref="L1"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId10"/>
-      <autoFilter ref="A2:P413" xr:uid="{BD5EE145-0813-46A7-BC75-B92AD019CB7F}"/>
+      <autoFilter ref="A2:P413" xr:uid="{C4DB4409-36DE-43A7-8BEC-0E95DAA096BC}"/>
     </customSheetView>
   </customSheetViews>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon\Documents\Meerkat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{56E75DFE-D236-4157-BB8E-71D06E06640A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{BDEDC571-FF32-43E4-A3F7-A8C4E1E1AAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3900" yWindow="3900" windowWidth="38700" windowHeight="15345" xr2:uid="{EB84704D-40C6-4DE5-9D9A-A41F237B8341}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{EB84704D-40C6-4DE5-9D9A-A41F237B8341}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning prod" sheetId="1" r:id="rId1"/>
@@ -868,16 +868,16 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
-    <customWorkbookView name="simon masurier - Affichage personnalisé" guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" mergeInterval="0" personalView="1" minimized="1" windowWidth="0" windowHeight="0" activeSheetId="1"/>
+    <customWorkbookView name="simon masurier - Affichage personnalisé" guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" mergeInterval="0" personalView="1" xWindow="-7" windowWidth="1734" windowHeight="1399" activeSheetId="1"/>
+    <customWorkbookView name="YOANN - Affichage personnalisé" guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}" autoUpdate="1" mergeInterval="15" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
+    <customWorkbookView name="SYLVAIN - Affichage personnalisé" guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
+    <customWorkbookView name="CEDRIC - Affichage personnalisé" guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}" mergeInterval="0" personalView="1" xWindow="873" yWindow="141" windowWidth="1874" windowHeight="1096" activeSheetId="1"/>
+    <customWorkbookView name="Commercial Commercial - Affichage personnalisé" guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1696" windowHeight="1026" activeSheetId="1"/>
+    <customWorkbookView name="SAEMT - Affichage personnalisé" guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}" mergeInterval="0" personalView="1" maximized="1" xWindow="-9" yWindow="-9" windowWidth="1938" windowHeight="1048" activeSheetId="1"/>
+    <customWorkbookView name="COMPTA2 - Affichage personnalisé" guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="COMPTA1 - Affichage personnalisé" guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="Production - Affichage personnalisé" guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}" mergeInterval="0" personalView="1" minimized="1" windowWidth="0" windowHeight="0" activeSheetId="1"/>
     <customWorkbookView name="Atelier - Affichage personnalisé" guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1696" windowHeight="1026" activeSheetId="1"/>
-    <customWorkbookView name="Production - Affichage personnalisé" guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}" mergeInterval="0" personalView="1" minimized="1" windowWidth="0" windowHeight="0" activeSheetId="1"/>
-    <customWorkbookView name="COMPTA1 - Affichage personnalisé" guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="COMPTA2 - Affichage personnalisé" guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="SAEMT - Affichage personnalisé" guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}" mergeInterval="0" personalView="1" maximized="1" xWindow="-9" yWindow="-9" windowWidth="1938" windowHeight="1048" activeSheetId="1"/>
-    <customWorkbookView name="Commercial Commercial - Affichage personnalisé" guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1696" windowHeight="1026" activeSheetId="1"/>
-    <customWorkbookView name="CEDRIC - Affichage personnalisé" guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}" mergeInterval="0" personalView="1" xWindow="873" yWindow="141" windowWidth="1874" windowHeight="1096" activeSheetId="1"/>
-    <customWorkbookView name="SYLVAIN - Affichage personnalisé" guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
-    <customWorkbookView name="YOANN - Affichage personnalisé" guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}" autoUpdate="1" mergeInterval="15" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4697,7 +4697,7 @@
 </file>
 
 <file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{1E54D5B1-1A9D-45B0-B660-700E91D70786}" diskRevisions="1" revisionId="125982" version="22">
+<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{A3A68CFF-FC26-4EBD-9192-1E52A48F7D2F}" diskRevisions="1" revisionId="125983" version="23">
   <header guid="{5369C422-BCF9-41A0-ACD4-6F1F3AA60B78}" dateTime="2025-04-17T18:17:38" maxSheetId="3" userName="simon masurier" r:id="rId10733">
     <sheetIdMap count="2">
       <sheetId val="1"/>
@@ -4819,6 +4819,12 @@
     </sheetIdMap>
   </header>
   <header guid="{1E54D5B1-1A9D-45B0-B660-700E91D70786}" dateTime="2025-04-17T20:43:42" maxSheetId="3" userName="simon masurier" r:id="rId10753" minRId="125977" maxRId="125981">
+    <sheetIdMap count="2">
+      <sheetId val="1"/>
+      <sheetId val="2"/>
+    </sheetIdMap>
+  </header>
+  <header guid="{A3A68CFF-FC26-4EBD-9192-1E52A48F7D2F}" dateTime="2025-04-17T21:09:33" maxSheetId="3" userName="simon masurier" r:id="rId10754">
     <sheetIdMap count="2">
       <sheetId val="1"/>
       <sheetId val="2"/>
@@ -5336,6 +5342,17 @@
       </is>
     </nc>
   </rcc>
+  <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="delete"/>
+  <rdn rId="0" localSheetId="1" customView="1" name="Z_FC992F80_D491_44A2_9044_1F3C55C8B0BF_.wvu.FilterData" hidden="1" oldHidden="1">
+    <formula>'Planning prod'!$A$2:$P$413</formula>
+    <oldFormula>'Planning prod'!$A$2:$P$413</oldFormula>
+  </rdn>
+  <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="add"/>
+</revisions>
+</file>
+
+<file path=xl/revisions/revisionLog21.xml><?xml version="1.0" encoding="utf-8"?>
+<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <rcv guid="{FC992F80-D491-44A2-9044-1F3C55C8B0BF}" action="delete"/>
   <rdn rId="0" localSheetId="1" customView="1" name="Z_FC992F80_D491_44A2_9044_1F3C55C8B0BF_.wvu.FilterData" hidden="1" oldHidden="1">
     <formula>'Planning prod'!$A$2:$P$413</formula>
@@ -58895,59 +58912,59 @@
       <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
       <autoFilter ref="A2:P413" xr:uid="{7722E3C6-80F5-4991-A518-5F8966A312D6}"/>
     </customSheetView>
-    <customSheetView guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}" scale="120" showPageBreaks="1" showAutoFilter="1" topLeftCell="A400">
-      <selection activeCell="A424" sqref="A424:XFD424"/>
+    <customSheetView guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}" scale="120" showAutoFilter="1" topLeftCell="C1">
+      <selection activeCell="L1" sqref="L1"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId2"/>
-      <autoFilter ref="A2:P413" xr:uid="{FA5FB3DF-CAA0-465A-AD54-2532FA7DD625}"/>
+      <autoFilter ref="A2:P413" xr:uid="{57D71931-A0CF-4AB9-96C9-84737A7736A2}"/>
     </customSheetView>
-    <customSheetView guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}" showPageBreaks="1" fitToPage="1" showAutoFilter="1" topLeftCell="A467">
-      <selection activeCell="E464" sqref="E464"/>
-      <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="8" scale="10" fitToHeight="0" orientation="portrait" r:id="rId3"/>
-      <autoFilter ref="A1:P364" xr:uid="{419441F1-66DA-474B-B1B5-36220848907E}"/>
+    <customSheetView guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}" scale="90" showAutoFilter="1" topLeftCell="D124">
+      <selection activeCell="I150" sqref="I150"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="8" orientation="landscape" r:id="rId3"/>
+      <autoFilter ref="A2:P473" xr:uid="{B7268AC9-D52C-4E6B-A8A4-175CA52D4A9F}"/>
+    </customSheetView>
+    <customSheetView guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}" scale="120" showAutoFilter="1" topLeftCell="A373">
+      <selection activeCell="A394" sqref="A394:D394"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="8" orientation="landscape" r:id="rId4"/>
+      <autoFilter ref="A2:P386" xr:uid="{3C5E1714-5449-40D9-BDCC-4FFA0887DF69}"/>
+    </customSheetView>
+    <customSheetView guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}" scale="120" topLeftCell="C211">
+      <selection activeCell="G234" sqref="G234"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="8" orientation="landscape" r:id="rId5"/>
+    </customSheetView>
+    <customSheetView guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}" showAutoFilter="1" topLeftCell="C391">
+      <selection activeCell="J487" sqref="J487"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="8" orientation="landscape" r:id="rId6"/>
+      <autoFilter ref="A1:P535" xr:uid="{D03F5E95-4B98-4361-9357-3C999914C96F}"/>
+    </customSheetView>
+    <customSheetView guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}" scale="120" showAutoFilter="1" topLeftCell="A444">
+      <selection activeCell="E482" sqref="E482"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="8" orientation="landscape" r:id="rId7"/>
+      <autoFilter ref="A2:P514" xr:uid="{67E61AC7-5740-4B95-BF19-BE41F8B586C2}"/>
     </customSheetView>
     <customSheetView guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}" scale="120" showAutoFilter="1">
       <pane ySplit="1" topLeftCell="A168" activePane="bottomLeft" state="frozen"/>
       <selection pane="bottomLeft" activeCell="A149" sqref="A149:XFD149"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="8" orientation="landscape" r:id="rId4"/>
-      <autoFilter ref="A2:P377" xr:uid="{620022E2-B9E4-43FE-B77D-7A1C1310119F}"/>
+      <pageSetup paperSize="8" orientation="landscape" r:id="rId8"/>
+      <autoFilter ref="A2:P377" xr:uid="{CF8FFF48-0891-4105-A2A9-DBEFC81AEB41}"/>
     </customSheetView>
-    <customSheetView guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}" scale="120" showAutoFilter="1" topLeftCell="A444">
-      <selection activeCell="E482" sqref="E482"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="8" orientation="landscape" r:id="rId5"/>
-      <autoFilter ref="A2:P514" xr:uid="{947DE699-CD34-422C-B707-1BEFE9DDDBA3}"/>
+    <customSheetView guid="{8349E4AD-CAB6-42BC-9560-953A009B1FCA}" showPageBreaks="1" fitToPage="1" showAutoFilter="1" topLeftCell="A467">
+      <selection activeCell="E464" sqref="E464"/>
+      <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="8" scale="10" fitToHeight="0" orientation="portrait" r:id="rId9"/>
+      <autoFilter ref="A1:P364" xr:uid="{05EB0939-BFD0-40AC-B99C-A865EB1E4312}"/>
     </customSheetView>
-    <customSheetView guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}" showAutoFilter="1" topLeftCell="C391">
-      <selection activeCell="J487" sqref="J487"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="8" orientation="landscape" r:id="rId6"/>
-      <autoFilter ref="A1:P535" xr:uid="{4AC187BA-5ACF-4F62-AE62-8E7120B1CCCD}"/>
-    </customSheetView>
-    <customSheetView guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}" scale="120" topLeftCell="C211">
-      <selection activeCell="G234" sqref="G234"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="8" orientation="landscape" r:id="rId7"/>
-    </customSheetView>
-    <customSheetView guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}" scale="120" showAutoFilter="1" topLeftCell="A373">
-      <selection activeCell="A394" sqref="A394:D394"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="8" orientation="landscape" r:id="rId8"/>
-      <autoFilter ref="A2:P386" xr:uid="{19AF686C-2C7A-4DDD-8100-72C2D0C4E56D}"/>
-    </customSheetView>
-    <customSheetView guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}" scale="90" showAutoFilter="1" topLeftCell="D124">
-      <selection activeCell="I150" sqref="I150"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="8" orientation="landscape" r:id="rId9"/>
-      <autoFilter ref="A2:P473" xr:uid="{58505C7A-7A70-4667-B2AE-A99094DE10BE}"/>
-    </customSheetView>
-    <customSheetView guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}" scale="120" showAutoFilter="1" topLeftCell="C1">
-      <selection activeCell="L1" sqref="L1"/>
+    <customSheetView guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}" scale="120" showPageBreaks="1" showAutoFilter="1" topLeftCell="A400">
+      <selection activeCell="A424" sqref="A424:XFD424"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="8" orientation="landscape" r:id="rId10"/>
-      <autoFilter ref="A2:P413" xr:uid="{C4DB4409-36DE-43A7-8BEC-0E95DAA096BC}"/>
+      <autoFilter ref="A2:P413" xr:uid="{A8F4AEEE-2E06-43BE-816B-2F54039E08A3}"/>
     </customSheetView>
   </customSheetViews>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -59016,7 +59033,31 @@
       <selection sqref="A1:D5"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
-    <customSheetView guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}">
+    <customSheetView guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}">
+      <selection sqref="A1:D5"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+    <customSheetView guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}">
       <selection sqref="A1:D5"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
@@ -59024,31 +59065,7 @@
       <selection sqref="A1:D5"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
-    <customSheetView guid="{B5F5A33D-7AAF-4F15-AA6E-B9763D554ED9}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{2429E9F7-33A7-4034-927E-05F85D5EE2C5}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{1B2B0C22-88FB-4A68-8147-E61DB54BAF10}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{A54BD138-D01F-44F1-886C-7975C9B22F9D}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{1E28EB69-245D-4435-BF94-0C240524C0B7}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{1AAB99C1-EBB3-4C01-BD10-4CC17FA9B1DF}">
-      <selection sqref="A1:D5"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{9040C179-6E44-4AF9-AE63-5EFF5C19CC72}">
+    <customSheetView guid="{A874E55E-EE34-4D09-98E8-0253D107FA9D}">
       <selection sqref="A1:D5"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
